--- a/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/model_use_case_review_checklist.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/model_use_case_review_checklist.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Partial</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>No</t>
         </is>
       </c>
     </row>
